--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:32:23+00:00</t>
+    <t>2026-09-16T15:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:06:55+00:00</t>
+    <t>2026-09-16T15:10:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:10:32+00:00</t>
+    <t>2026-09-16T15:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
+++ b/nr-doc-core-procedure/ig/ValueSet-fr-core-vs-heartrate-body-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T15:30:48+00:00</t>
+    <t>2026-09-17T13:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
